--- a/data/notifications.xlsx
+++ b/data/notifications.xlsx
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TP015826</t>
+          <t>TP083880</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Test Student 4</t>
+          <t>Yoon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,24 +486,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15-10-2026 10:48</t>
+          <t>20-10-2026 15:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TP015826</t>
+          <t>TP083880</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Test Student 4</t>
+          <t>Yoon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15-10-2026 10:48</t>
+          <t>20-10-2026 15:48</t>
         </is>
       </c>
     </row>
